--- a/test-automation/EN301549v4.1.1-web-automation-matrix.en.xlsx
+++ b/test-automation/EN301549v4.1.1-web-automation-matrix.en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\a11y-best-practices\test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AA4651-32D4-444C-93DC-BADC93A3F184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44206CB4-A744-4F9D-A505-FD7F225E0E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5115" yWindow="-21600" windowWidth="26010" windowHeight="21705" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21780" yWindow="-21600" windowWidth="26010" windowHeight="21705" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foreword" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="278">
   <si>
     <t>5.1.2.1 Closed functionality</t>
   </si>
@@ -946,6 +946,18 @@
   </si>
   <si>
     <t>Sum for (shall)</t>
+  </si>
+  <si>
+    <t>WAVE</t>
+  </si>
+  <si>
+    <t>miCheck</t>
+  </si>
+  <si>
+    <t>Accessibility Insights</t>
+  </si>
+  <si>
+    <t>Föll (2026):ja</t>
   </si>
 </sst>
 </file>
@@ -957,6 +969,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1087,12 +1106,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1198,143 +1211,145 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0"/>
   </cellStyleXfs>
   <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1344,14 +1359,7 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="41">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color theme="1"/>
@@ -1393,263 +1401,6 @@
         <patternFill patternType="solid">
           <fgColor theme="7" tint="0.59996337778862885"/>
           <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7" tint="0.59996337778862885"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7" tint="0.59996337778862885"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7" tint="0.59996337778862885"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1972,7 +1723,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>164</v>
       </c>
@@ -1988,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45DBFE1-9182-487E-B9F3-380D45B58EC5}">
-  <dimension ref="A1:AC201"/>
+  <dimension ref="A1:EL201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="46.46484375" customWidth="1"/>
@@ -1998,10 +1749,9 @@
     <col min="5" max="6" width="12.46484375" style="7" customWidth="1"/>
     <col min="7" max="7" width="11.265625" style="7" customWidth="1"/>
     <col min="8" max="12" width="11.265625" customWidth="1"/>
-    <col min="13" max="14" width="6.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="11" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:142" s="11" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>192</v>
       </c>
@@ -2032,10 +1782,146 @@
       <c r="J1" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K1" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="M1" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="59"/>
+      <c r="AB1" s="59"/>
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="59"/>
+      <c r="AI1" s="59"/>
+      <c r="AJ1" s="59"/>
+      <c r="AK1" s="59"/>
+      <c r="AL1" s="59"/>
+      <c r="AM1" s="59"/>
+      <c r="AN1" s="59"/>
+      <c r="AO1" s="59"/>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="59"/>
+      <c r="AR1" s="59"/>
+      <c r="AS1" s="59"/>
+      <c r="AT1" s="59"/>
+      <c r="AU1" s="59"/>
+      <c r="AV1" s="59"/>
+      <c r="AW1" s="59"/>
+      <c r="AX1" s="59"/>
+      <c r="AY1" s="59"/>
+      <c r="AZ1" s="59"/>
+      <c r="BA1" s="59"/>
+      <c r="BB1" s="59"/>
+      <c r="BC1" s="59"/>
+      <c r="BD1" s="59"/>
+      <c r="BE1" s="59"/>
+      <c r="BF1" s="59"/>
+      <c r="BG1" s="59"/>
+      <c r="BH1" s="59"/>
+      <c r="BI1" s="59"/>
+      <c r="BJ1" s="59"/>
+      <c r="BK1" s="59"/>
+      <c r="BL1" s="59"/>
+      <c r="BM1" s="59"/>
+      <c r="BN1" s="59"/>
+      <c r="BO1" s="59"/>
+      <c r="BP1" s="59"/>
+      <c r="BQ1" s="59"/>
+      <c r="BR1" s="59"/>
+      <c r="BS1" s="59"/>
+      <c r="BT1" s="59"/>
+      <c r="BU1" s="59"/>
+      <c r="BV1" s="59"/>
+      <c r="BW1" s="59"/>
+      <c r="BX1" s="59"/>
+      <c r="BY1" s="59"/>
+      <c r="BZ1" s="59"/>
+      <c r="CA1" s="59"/>
+      <c r="CB1" s="59"/>
+      <c r="CC1" s="59"/>
+      <c r="CD1" s="59"/>
+      <c r="CE1" s="59"/>
+      <c r="CF1" s="59"/>
+      <c r="CG1" s="59"/>
+      <c r="CH1" s="59"/>
+      <c r="CI1" s="59"/>
+      <c r="CJ1" s="59"/>
+      <c r="CK1" s="59"/>
+      <c r="CL1" s="59"/>
+      <c r="CM1" s="59"/>
+      <c r="CN1" s="59"/>
+      <c r="CO1" s="59"/>
+      <c r="CP1" s="59"/>
+      <c r="CQ1" s="59"/>
+      <c r="CR1" s="59"/>
+      <c r="CS1" s="59"/>
+      <c r="CT1" s="59"/>
+      <c r="CU1" s="59"/>
+      <c r="CV1" s="59"/>
+      <c r="CW1" s="59"/>
+      <c r="CX1" s="59"/>
+      <c r="CY1" s="59"/>
+      <c r="CZ1" s="59"/>
+      <c r="DA1" s="59"/>
+      <c r="DB1" s="59"/>
+      <c r="DC1" s="59"/>
+      <c r="DD1" s="59"/>
+      <c r="DE1" s="59"/>
+      <c r="DF1" s="59"/>
+      <c r="DG1" s="59"/>
+      <c r="DH1" s="59"/>
+      <c r="DI1" s="59"/>
+      <c r="DJ1" s="59"/>
+      <c r="DK1" s="59"/>
+      <c r="DL1" s="59"/>
+      <c r="DM1" s="59"/>
+      <c r="DN1" s="59"/>
+      <c r="DO1" s="59"/>
+      <c r="DP1" s="59"/>
+      <c r="DQ1" s="59"/>
+      <c r="DR1" s="59"/>
+      <c r="DS1" s="59"/>
+      <c r="DT1" s="59"/>
+      <c r="DU1" s="59"/>
+      <c r="DV1" s="59"/>
+      <c r="DW1" s="59"/>
+      <c r="DX1" s="59"/>
+      <c r="DY1" s="59"/>
+      <c r="DZ1" s="59"/>
+      <c r="EA1" s="59"/>
+      <c r="EB1" s="59"/>
+      <c r="EC1" s="59"/>
+      <c r="ED1" s="59"/>
+      <c r="EE1" s="59"/>
+      <c r="EF1" s="59"/>
+      <c r="EG1" s="59"/>
+      <c r="EH1" s="59"/>
+      <c r="EI1" s="59"/>
+      <c r="EJ1" s="59"/>
+      <c r="EK1" s="59"/>
+      <c r="EL1" s="59"/>
+    </row>
+    <row r="2" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
@@ -2043,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
@@ -2051,7 +1937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A4" s="17" t="s">
         <v>3</v>
       </c>
@@ -2059,7 +1945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A5" s="17" t="s">
         <v>4</v>
       </c>
@@ -2067,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A6" s="17" t="s">
         <v>5</v>
       </c>
@@ -2075,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A7" s="17" t="s">
         <v>6</v>
       </c>
@@ -2083,7 +1969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A8" s="17" t="s">
         <v>7</v>
       </c>
@@ -2091,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
         <v>8</v>
       </c>
@@ -2099,7 +1985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
         <v>9</v>
       </c>
@@ -2107,7 +1993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A11" s="17" t="s">
         <v>10</v>
       </c>
@@ -2115,7 +2001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A12" s="17" t="s">
         <v>11</v>
       </c>
@@ -2123,7 +2009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A13" s="17" t="s">
         <v>12</v>
       </c>
@@ -2131,7 +2017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A14" s="17" t="s">
         <v>13</v>
       </c>
@@ -2139,7 +2025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A15" s="17" t="s">
         <v>14</v>
       </c>
@@ -2147,7 +2033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A16" s="17" t="s">
         <v>15</v>
       </c>
@@ -2771,7 +2657,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A81" s="17" t="s">
         <v>79</v>
       </c>
@@ -2785,7 +2671,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A82" s="17" t="s">
         <v>80</v>
       </c>
@@ -2799,7 +2685,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A83" s="17" t="s">
         <v>81</v>
       </c>
@@ -2811,7 +2697,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A84" s="17" t="s">
         <v>82</v>
       </c>
@@ -2825,7 +2711,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A85" s="22" t="s">
         <v>83</v>
       </c>
@@ -2856,8 +2742,17 @@
       <c r="J85" s="6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="K85" t="s">
+        <v>277</v>
+      </c>
+      <c r="L85" t="s">
+        <v>277</v>
+      </c>
+      <c r="M85" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A86" s="22" t="s">
         <v>84</v>
       </c>
@@ -2877,7 +2772,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A87" s="22" t="s">
         <v>85</v>
       </c>
@@ -2890,8 +2785,11 @@
       <c r="D87" s="23" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K87" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A88" s="22" t="s">
         <v>86</v>
       </c>
@@ -2905,7 +2803,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A89" s="22" t="s">
         <v>87</v>
       </c>
@@ -2919,7 +2817,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A90" s="22" t="s">
         <v>88</v>
       </c>
@@ -2933,7 +2831,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A91" s="34" t="s">
         <v>210</v>
       </c>
@@ -2950,7 +2848,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
     </row>
-    <row r="92" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A92" s="34" t="s">
         <v>212</v>
       </c>
@@ -2967,7 +2865,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
     </row>
-    <row r="93" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A93" s="36" t="s">
         <v>213</v>
       </c>
@@ -2984,7 +2882,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
     </row>
-    <row r="94" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A94" s="36" t="s">
         <v>214</v>
       </c>
@@ -3001,7 +2899,7 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
     </row>
-    <row r="95" spans="1:10" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A95" s="22" t="s">
         <v>89</v>
       </c>
@@ -3026,8 +2924,17 @@
       <c r="J95" s="9" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K95" t="s">
+        <v>277</v>
+      </c>
+      <c r="L95" t="s">
+        <v>277</v>
+      </c>
+      <c r="M95" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A96" s="22" t="s">
         <v>90</v>
       </c>
@@ -3039,8 +2946,11 @@
         <v>200</v>
       </c>
       <c r="J96" s="8"/>
-    </row>
-    <row r="97" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="K96" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A97" s="22" t="s">
         <v>91</v>
       </c>
@@ -3057,7 +2967,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A98" s="22" t="s">
         <v>92</v>
       </c>
@@ -3071,7 +2981,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A99" s="22" t="s">
         <v>93</v>
       </c>
@@ -3084,8 +2994,11 @@
       <c r="D99" s="33" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="M99" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="36" t="s">
         <v>220</v>
       </c>
@@ -3102,7 +3015,7 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
     </row>
-    <row r="101" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A101" s="22" t="s">
         <v>94</v>
       </c>
@@ -3118,8 +3031,11 @@
       <c r="E101" s="24" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+      <c r="M101" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A102" s="22" t="s">
         <v>95</v>
       </c>
@@ -3138,8 +3054,14 @@
       <c r="G102" s="24" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+      <c r="K102" t="s">
+        <v>277</v>
+      </c>
+      <c r="L102" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A103" s="22" t="s">
         <v>96</v>
       </c>
@@ -3161,8 +3083,17 @@
       <c r="G103" s="24" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+      <c r="K103" t="s">
+        <v>277</v>
+      </c>
+      <c r="L103" t="s">
+        <v>277</v>
+      </c>
+      <c r="M103" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A104" s="22" t="s">
         <v>97</v>
       </c>
@@ -3185,7 +3116,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A105" s="22" t="s">
         <v>98</v>
       </c>
@@ -3199,7 +3130,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A106" s="34" t="s">
         <v>229</v>
       </c>
@@ -3216,7 +3147,7 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
     </row>
-    <row r="107" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A107" s="34" t="s">
         <v>230</v>
       </c>
@@ -3233,7 +3164,7 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
     </row>
-    <row r="108" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A108" s="34" t="s">
         <v>231</v>
       </c>
@@ -3250,7 +3181,7 @@
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
     </row>
-    <row r="109" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A109" s="34" t="s">
         <v>232</v>
       </c>
@@ -3267,7 +3198,7 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A110" s="22" t="s">
         <v>99</v>
       </c>
@@ -3281,7 +3212,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A111" s="22" t="s">
         <v>100</v>
       </c>
@@ -3295,7 +3226,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A112" s="22" t="s">
         <v>101</v>
       </c>
@@ -3309,7 +3240,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A113" s="22" t="s">
         <v>102</v>
       </c>
@@ -3323,7 +3254,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A114" s="22" t="s">
         <v>103</v>
       </c>
@@ -3339,8 +3270,14 @@
       <c r="J114" s="6" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K114" t="s">
+        <v>277</v>
+      </c>
+      <c r="L114" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A115" s="22" t="s">
         <v>104</v>
       </c>
@@ -3354,7 +3291,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A116" s="34" t="s">
         <v>237</v>
       </c>
@@ -3371,7 +3308,7 @@
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A117" s="22" t="s">
         <v>105</v>
       </c>
@@ -3385,7 +3322,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A118" s="22" t="s">
         <v>106</v>
       </c>
@@ -3399,7 +3336,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A119" s="22" t="s">
         <v>107</v>
       </c>
@@ -3413,7 +3350,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A120" s="34" t="s">
         <v>238</v>
       </c>
@@ -3430,7 +3367,7 @@
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
     </row>
-    <row r="121" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A121" s="36" t="s">
         <v>239</v>
       </c>
@@ -3447,7 +3384,7 @@
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
     </row>
-    <row r="122" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A122" s="34" t="s">
         <v>240</v>
       </c>
@@ -3464,7 +3401,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
     </row>
-    <row r="123" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A123" s="34" t="s">
         <v>242</v>
       </c>
@@ -3481,7 +3418,7 @@
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A124" s="22" t="s">
         <v>108</v>
       </c>
@@ -3495,7 +3432,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="125" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A125" s="34" t="s">
         <v>243</v>
       </c>
@@ -3512,7 +3449,7 @@
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
     </row>
-    <row r="126" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A126" s="34" t="s">
         <v>244</v>
       </c>
@@ -3529,7 +3466,7 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A127" s="22" t="s">
         <v>109</v>
       </c>
@@ -3542,8 +3479,11 @@
       <c r="D127" s="33" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K127" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A128" s="22" t="s">
         <v>110</v>
       </c>
@@ -3559,8 +3499,17 @@
       <c r="I128" s="5" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="K128" t="s">
+        <v>277</v>
+      </c>
+      <c r="L128" t="s">
+        <v>277</v>
+      </c>
+      <c r="M128" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A129" s="22" t="s">
         <v>111</v>
       </c>
@@ -3574,8 +3523,14 @@
         <v>247</v>
       </c>
       <c r="I129" s="5"/>
-    </row>
-    <row r="130" spans="1:9" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="K129" t="s">
+        <v>277</v>
+      </c>
+      <c r="M129" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A130" s="22" t="s">
         <v>112</v>
       </c>
@@ -3601,7 +3556,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A131" s="22" t="s">
         <v>113</v>
       </c>
@@ -3616,7 +3571,7 @@
       </c>
       <c r="I131" s="5"/>
     </row>
-    <row r="132" spans="1:9" ht="57" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:13" ht="57" x14ac:dyDescent="0.45">
       <c r="A132" s="22" t="s">
         <v>114</v>
       </c>
@@ -3636,7 +3591,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A133" s="22" t="s">
         <v>115</v>
       </c>
@@ -3650,7 +3605,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="134" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A134" s="34" t="s">
         <v>250</v>
       </c>
@@ -3665,7 +3620,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
     </row>
-    <row r="135" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A135" s="34" t="s">
         <v>251</v>
       </c>
@@ -3680,7 +3635,7 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
     </row>
-    <row r="136" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A136" s="34" t="s">
         <v>252</v>
       </c>
@@ -3697,7 +3652,7 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
     </row>
-    <row r="137" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A137" s="40" t="s">
         <v>116</v>
       </c>
@@ -3709,7 +3664,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
     </row>
-    <row r="138" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A138" s="34" t="s">
         <v>253</v>
       </c>
@@ -3721,7 +3676,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
     </row>
-    <row r="139" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A139" s="34" t="s">
         <v>254</v>
       </c>
@@ -3733,7 +3688,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A140" s="22" t="s">
         <v>117</v>
       </c>
@@ -3747,7 +3702,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A141" s="22" t="s">
         <v>118</v>
       </c>
@@ -3761,7 +3716,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A142" s="22" t="s">
         <v>119</v>
       </c>
@@ -3774,8 +3729,11 @@
       <c r="D142" s="33" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="M142" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A143" s="22" t="s">
         <v>120</v>
       </c>
@@ -3789,7 +3747,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="144" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A144" s="34" t="s">
         <v>255</v>
       </c>
@@ -3804,7 +3762,7 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
     </row>
-    <row r="145" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A145" s="34" t="s">
         <v>256</v>
       </c>
@@ -3821,7 +3779,7 @@
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
     </row>
-    <row r="146" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A146" s="40" t="s">
         <v>121</v>
       </c>
@@ -3833,7 +3791,7 @@
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
     </row>
-    <row r="147" spans="1:10" s="29" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:13" s="29" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A147" s="40" t="s">
         <v>122</v>
       </c>
@@ -3851,7 +3809,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A148" s="22" t="s">
         <v>123</v>
       </c>
@@ -3877,8 +3835,17 @@
         <v>172</v>
       </c>
       <c r="J148" s="8"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K148" t="s">
+        <v>277</v>
+      </c>
+      <c r="L148" t="s">
+        <v>277</v>
+      </c>
+      <c r="M148" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A149" s="22" t="s">
         <v>124</v>
       </c>
@@ -3898,7 +3865,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A150" s="34" t="s">
         <v>258</v>
       </c>
@@ -3915,7 +3882,7 @@
       <c r="F150" s="8"/>
       <c r="G150" s="8"/>
     </row>
-    <row r="151" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A151" s="34" t="s">
         <v>259</v>
       </c>
@@ -3932,7 +3899,7 @@
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
     </row>
-    <row r="152" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A152" s="34" t="s">
         <v>260</v>
       </c>
@@ -3949,7 +3916,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
     </row>
-    <row r="153" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A153" s="34" t="s">
         <v>262</v>
       </c>
@@ -3966,7 +3933,7 @@
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A154" s="22" t="s">
         <v>125</v>
       </c>
@@ -3980,7 +3947,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A155" s="22" t="s">
         <v>126</v>
       </c>
@@ -3993,8 +3960,11 @@
       <c r="D155" s="23" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K155" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A156" s="22" t="s">
         <v>127</v>
       </c>
@@ -4008,7 +3978,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A157" s="22" t="s">
         <v>128</v>
       </c>
@@ -4022,7 +3992,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="158" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A158" s="34" t="s">
         <v>263</v>
       </c>
@@ -4037,7 +4007,7 @@
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
     </row>
-    <row r="159" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A159" s="40" t="s">
         <v>129</v>
       </c>
@@ -4049,7 +4019,7 @@
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A160" s="22" t="s">
         <v>130</v>
       </c>
@@ -4063,7 +4033,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A161" s="22" t="s">
         <v>131</v>
       </c>
@@ -4077,7 +4047,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A162" s="22" t="s">
         <v>132</v>
       </c>
@@ -4094,7 +4064,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A163" s="22" t="s">
         <v>133</v>
       </c>
@@ -4108,7 +4078,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="164" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A164" s="34" t="s">
         <v>264</v>
       </c>
@@ -4123,7 +4093,7 @@
       <c r="F164" s="8"/>
       <c r="G164" s="8"/>
     </row>
-    <row r="165" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A165" s="34" t="s">
         <v>265</v>
       </c>
@@ -4138,7 +4108,7 @@
       <c r="F165" s="8"/>
       <c r="G165" s="8"/>
     </row>
-    <row r="166" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A166" s="40" t="s">
         <v>134</v>
       </c>
@@ -4150,7 +4120,7 @@
       <c r="F166" s="8"/>
       <c r="G166" s="8"/>
     </row>
-    <row r="167" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A167" s="40" t="s">
         <v>135</v>
       </c>
@@ -4162,7 +4132,7 @@
       <c r="F167" s="8"/>
       <c r="G167" s="8"/>
     </row>
-    <row r="168" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A168" s="34" t="s">
         <v>266</v>
       </c>
@@ -4174,7 +4144,7 @@
       <c r="F168" s="8"/>
       <c r="G168" s="8"/>
     </row>
-    <row r="169" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A169" s="22" t="s">
         <v>136</v>
       </c>
@@ -4193,8 +4163,17 @@
       <c r="G169" s="24" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K169" t="s">
+        <v>277</v>
+      </c>
+      <c r="L169" t="s">
+        <v>277</v>
+      </c>
+      <c r="M169" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A170" s="22" t="s">
         <v>137</v>
       </c>
@@ -4205,7 +4184,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A171" s="22" t="s">
         <v>138</v>
       </c>
@@ -4213,7 +4192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A172" s="31" t="s">
         <v>139</v>
       </c>
@@ -4227,7 +4206,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A173" s="22" t="s">
         <v>141</v>
       </c>
@@ -4241,7 +4220,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A174" s="22" t="s">
         <v>142</v>
       </c>
@@ -4255,7 +4234,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A175" s="22" t="s">
         <v>143</v>
       </c>
@@ -4269,7 +4248,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A176" s="31" t="s">
         <v>144</v>
       </c>
@@ -4425,7 +4404,7 @@
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A193" s="55" t="s">
+      <c r="A193" t="s">
         <v>268</v>
       </c>
       <c r="B193" s="20" t="s">
@@ -4448,7 +4427,7 @@
         <f>COUNTIFS($B$2:$B$194,"=A",C$2:C$194,"*")</f>
         <v>27</v>
       </c>
-      <c r="D195" s="56">
+      <c r="D195" s="55">
         <f t="shared" ref="D195:J195" si="0">COUNTIFS($B$2:$B$194,"=A",D$2:D$194,"*")</f>
         <v>29</v>
       </c>
@@ -4489,7 +4468,7 @@
         <f>COUNTIFS($B$2:$B$194,"=AA",C$2:C$194,"*")</f>
         <v>19</v>
       </c>
-      <c r="D196" s="57">
+      <c r="D196" s="56">
         <f t="shared" ref="D196:J196" si="1">COUNTIFS($B$2:$B$194,"=AA",D$2:D$194,"*")</f>
         <v>20</v>
       </c>
@@ -4529,7 +4508,7 @@
       <c r="C197" s="51">
         <v>0</v>
       </c>
-      <c r="D197" s="58">
+      <c r="D197" s="57">
         <v>1</v>
       </c>
       <c r="E197" s="51">
@@ -4563,7 +4542,7 @@
         <f>COUNTIFS($B$2:$B$194,"=shall",C$2:C$194,"*")</f>
         <v>12</v>
       </c>
-      <c r="D198" s="57">
+      <c r="D198" s="56">
         <f t="shared" ref="D198:J198" si="2">COUNTIFS($B$2:$B$194,"=shall",D$2:D$194,"*")</f>
         <v>35</v>
       </c>
@@ -4603,7 +4582,7 @@
       <c r="C199" s="53">
         <v>0</v>
       </c>
-      <c r="D199" s="59">
+      <c r="D199" s="58">
         <v>1</v>
       </c>
       <c r="E199" s="53">
@@ -4742,29 +4721,29 @@
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A189:A193">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C172:C175">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:D1 C27 D54:D56 D76:D99 C76:C136 C140:C145 C148:C158 C160:C165 C189:C191 C219:C1048576 C195:J199">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
+  <conditionalFormatting sqref="C1:D1 C27 D54:D56 C76:D136 C140:C145 C148:C158 C160:C165 C189:C191 C195:J199 C219:C1048576">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26">
-    <cfRule type="cellIs" dxfId="2" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
       <formula>"nicht abgedeckt"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D66:D73 D100:D136 D26:D28 D48 D51:D52 D60 D140:D154">
-    <cfRule type="cellIs" dxfId="1" priority="20" operator="equal">
+  <conditionalFormatting sqref="D26:D28 D48 D51:D52 D60 D66:D73 D140:D154">
+    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
       <formula>"manuell"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A189:A193">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157500000008" bottom="0.78740157500000008" header="0.3" footer="0.3"/>

--- a/test-automation/EN301549v4.1.1-web-automation-matrix.en.xlsx
+++ b/test-automation/EN301549v4.1.1-web-automation-matrix.en.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\a11y-best-practices\test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44206CB4-A744-4F9D-A505-FD7F225E0E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2516E7A-E2E8-4C0E-8CB3-D2D42A22D362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21780" yWindow="-21600" windowWidth="26010" windowHeight="21705" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5130" yWindow="-21720" windowWidth="51840" windowHeight="21840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foreword" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Web!$A$1:$C$193</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -53,7 +53,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>https://www.etsi.org/deliver/etsi_en/301500_301599/301549/04.01.00_30/en_301549v040100va.pdf</t>
         </r>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="282">
   <si>
     <t>5.1.2.1 Closed functionality</t>
   </si>
@@ -662,9 +662,6 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Meaning</t>
-  </si>
-  <si>
     <t>True positive, with correct location information</t>
   </si>
   <si>
@@ -672,9 +669,6 @@
   </si>
   <si>
     <t>False positive, with relevant location information</t>
-  </si>
-  <si>
-    <t>False positive, with no or irrelevant location information</t>
   </si>
   <si>
     <t>Factor 0.5 for warnings (rather than errors)</t>
@@ -958,6 +952,24 @@
   </si>
   <si>
     <t>Föll (2026):ja</t>
+  </si>
+  <si>
+    <t>False negative</t>
+  </si>
+  <si>
+    <t>Meaning wrt positives</t>
+  </si>
+  <si>
+    <t>Meaning wrt negatives</t>
+  </si>
+  <si>
+    <t>True negative</t>
+  </si>
+  <si>
+    <t>False positive, with no or irrelevant/false location information</t>
+  </si>
+  <si>
+    <t>This scale is understood as interval scale, i.e. arithmetic means can be computed.</t>
   </si>
 </sst>
 </file>
@@ -986,10 +998,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -997,6 +1017,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1004,23 +1025,27 @@
       <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="7" tint="-0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1047,11 +1072,13 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="65"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1072,11 +1099,13 @@
       <sz val="11"/>
       <color rgb="FF806000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1085,13 +1114,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1211,146 +1233,148 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1723,7 +1747,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>164</v>
       </c>
@@ -1753,25 +1777,25 @@
   <sheetData>
     <row r="1" spans="1:142" s="11" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="E1" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>196</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>166</v>
@@ -1780,16 +1804,16 @@
         <v>165</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K1" s="59" t="s">
+        <v>272</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>273</v>
+      </c>
+      <c r="M1" s="59" t="s">
         <v>274</v>
-      </c>
-      <c r="L1" s="59" t="s">
-        <v>275</v>
-      </c>
-      <c r="M1" s="59" t="s">
-        <v>276</v>
       </c>
       <c r="N1" s="59"/>
       <c r="O1" s="59"/>
@@ -2121,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E26" s="24"/>
     </row>
@@ -2133,10 +2157,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
@@ -2147,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
@@ -2198,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
@@ -2209,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
@@ -2220,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
@@ -2231,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
@@ -2242,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
@@ -2325,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
@@ -2352,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
@@ -2363,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
@@ -2382,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -2393,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
@@ -2404,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
@@ -2439,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
@@ -2490,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
@@ -2501,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
@@ -2512,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
@@ -2523,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
@@ -2534,7 +2558,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
@@ -2545,18 +2569,18 @@
         <v>1</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B72" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -2567,7 +2591,7 @@
         <v>140</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
@@ -2594,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
@@ -2611,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
@@ -2626,7 +2650,7 @@
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
@@ -2637,10 +2661,10 @@
         <v>1</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
@@ -2651,10 +2675,10 @@
         <v>1</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.45">
@@ -2665,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.45">
@@ -2679,10 +2703,10 @@
         <v>1</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.45">
@@ -2694,7 +2718,7 @@
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.45">
@@ -2705,10 +2729,10 @@
         <v>1</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="57" x14ac:dyDescent="0.45">
@@ -2716,22 +2740,22 @@
         <v>83</v>
       </c>
       <c r="B85" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="C85" s="32" t="s">
+      <c r="E85" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="D85" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E85" s="24" t="s">
-        <v>208</v>
-      </c>
       <c r="F85" s="24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H85" s="9" t="s">
         <v>176</v>
@@ -2743,13 +2767,13 @@
         <v>168</v>
       </c>
       <c r="K85" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L85" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M85" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
@@ -2757,16 +2781,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>177</v>
@@ -2777,16 +2801,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K87" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.45">
@@ -2794,13 +2818,13 @@
         <v>86</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.45">
@@ -2808,13 +2832,13 @@
         <v>87</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.45">
@@ -2822,27 +2846,27 @@
         <v>88</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A91" s="34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -2850,16 +2874,16 @@
     </row>
     <row r="92" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A92" s="34" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -2867,16 +2891,16 @@
     </row>
     <row r="93" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A93" s="36" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
@@ -2884,16 +2908,16 @@
     </row>
     <row r="94" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A94" s="36" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D94" s="33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
@@ -2904,34 +2928,34 @@
         <v>89</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C95" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="D95" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E95" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="D95" s="33" t="s">
+      <c r="F95" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="G95" s="24" t="s">
         <v>217</v>
-      </c>
-      <c r="E95" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="F95" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="G95" s="24" t="s">
-        <v>219</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>169</v>
       </c>
       <c r="K95" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L95" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M95" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.45">
@@ -2939,15 +2963,15 @@
         <v>90</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C96" s="25"/>
       <c r="D96" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
@@ -2955,13 +2979,13 @@
         <v>91</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>170</v>
@@ -2972,13 +2996,13 @@
         <v>92</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.45">
@@ -2986,30 +3010,30 @@
         <v>93</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D99" s="33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M99" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="36" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D100" s="33" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -3020,19 +3044,19 @@
         <v>94</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C101" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D101" s="33" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E101" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M101" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="57" x14ac:dyDescent="0.45">
@@ -3040,25 +3064,25 @@
         <v>95</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K102" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L102" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="57" x14ac:dyDescent="0.45">
@@ -3066,31 +3090,31 @@
         <v>96</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C103" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="D103" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E103" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="F103" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="G103" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="E103" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="F103" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="G103" s="24" t="s">
-        <v>226</v>
-      </c>
       <c r="K103" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L103" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M103" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="57" x14ac:dyDescent="0.45">
@@ -3098,22 +3122,22 @@
         <v>97</v>
       </c>
       <c r="B104" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C104" s="32" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E104" s="24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G104" s="24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.45">
@@ -3121,27 +3145,27 @@
         <v>98</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A106" s="34" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
@@ -3149,16 +3173,16 @@
     </row>
     <row r="107" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A107" s="34" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C107" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
@@ -3166,16 +3190,16 @@
     </row>
     <row r="108" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A108" s="34" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C108" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
@@ -3183,16 +3207,16 @@
     </row>
     <row r="109" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A109" s="34" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C109" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
@@ -3203,13 +3227,13 @@
         <v>99</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C110" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D110" s="33" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.45">
@@ -3217,13 +3241,13 @@
         <v>100</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C111" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D111" s="33" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.45">
@@ -3231,13 +3255,13 @@
         <v>101</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C112" s="32" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.45">
@@ -3245,13 +3269,13 @@
         <v>102</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D113" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
@@ -3259,22 +3283,22 @@
         <v>103</v>
       </c>
       <c r="B114" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C114" s="32" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D114" s="23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J114" s="6" t="s">
         <v>171</v>
       </c>
       <c r="K114" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L114" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.45">
@@ -3282,27 +3306,27 @@
         <v>104</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A116" s="34" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C116" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
@@ -3313,13 +3337,13 @@
         <v>105</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D117" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.45">
@@ -3327,13 +3351,13 @@
         <v>106</v>
       </c>
       <c r="B118" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D118" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.45">
@@ -3341,27 +3365,27 @@
         <v>107</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A120" s="34" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B120" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
@@ -3369,16 +3393,16 @@
     </row>
     <row r="121" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A121" s="36" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C121" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D121" s="38" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
@@ -3386,16 +3410,16 @@
     </row>
     <row r="122" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A122" s="34" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C122" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D122" s="38" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
@@ -3403,16 +3427,16 @@
     </row>
     <row r="123" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A123" s="34" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C123" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D123" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
@@ -3423,27 +3447,27 @@
         <v>108</v>
       </c>
       <c r="B124" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D124" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="125" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A125" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C125" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
@@ -3451,16 +3475,16 @@
     </row>
     <row r="126" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A126" s="34" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B126" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C126" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D126" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
@@ -3471,16 +3495,16 @@
         <v>109</v>
       </c>
       <c r="B127" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C127" s="32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D127" s="33" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K127" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.45">
@@ -3488,25 +3512,25 @@
         <v>110</v>
       </c>
       <c r="B128" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D128" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>172</v>
       </c>
       <c r="K128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.45">
@@ -3514,20 +3538,20 @@
         <v>111</v>
       </c>
       <c r="B129" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C129" s="39" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D129" s="33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I129" s="5"/>
       <c r="K129" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M129" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
@@ -3535,22 +3559,22 @@
         <v>112</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C130" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D130" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E130" s="24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G130" s="24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>172</v>
@@ -3561,13 +3585,13 @@
         <v>113</v>
       </c>
       <c r="B131" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C131" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D131" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I131" s="5"/>
     </row>
@@ -3576,16 +3600,16 @@
         <v>114</v>
       </c>
       <c r="B132" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C132" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D132" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G132" s="24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>172</v>
@@ -3596,24 +3620,24 @@
         <v>115</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C133" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="134" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A134" s="34" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B134" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C134" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D134" s="30"/>
       <c r="E134" s="8"/>
@@ -3622,13 +3646,13 @@
     </row>
     <row r="135" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A135" s="34" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B135" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C135" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D135" s="30"/>
       <c r="E135" s="8"/>
@@ -3637,16 +3661,16 @@
     </row>
     <row r="136" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A136" s="34" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B136" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C136" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D136" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
@@ -3657,7 +3681,7 @@
         <v>116</v>
       </c>
       <c r="B137" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D137" s="42"/>
       <c r="E137" s="8"/>
@@ -3666,10 +3690,10 @@
     </row>
     <row r="138" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A138" s="34" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B138" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="8"/>
@@ -3678,10 +3702,10 @@
     </row>
     <row r="139" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A139" s="34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B139" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D139" s="43"/>
       <c r="E139" s="8"/>
@@ -3693,13 +3717,13 @@
         <v>117</v>
       </c>
       <c r="B140" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C140" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D140" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.45">
@@ -3707,13 +3731,13 @@
         <v>118</v>
       </c>
       <c r="B141" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C141" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.45">
@@ -3721,16 +3745,16 @@
         <v>119</v>
       </c>
       <c r="B142" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C142" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D142" s="33" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M142" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.45">
@@ -3738,24 +3762,24 @@
         <v>120</v>
       </c>
       <c r="B143" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D143" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A144" s="34" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C144" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D144" s="30"/>
       <c r="E144" s="8"/>
@@ -3764,16 +3788,16 @@
     </row>
     <row r="145" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A145" s="34" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C145" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D145" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
@@ -3784,7 +3808,7 @@
         <v>121</v>
       </c>
       <c r="B146" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D146" s="30"/>
       <c r="E146" s="8"/>
@@ -3796,17 +3820,17 @@
         <v>122</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D147" s="30"/>
       <c r="E147" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
@@ -3814,35 +3838,35 @@
         <v>123</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C148" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D148" s="33" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E148" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G148" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>172</v>
       </c>
       <c r="J148" s="8"/>
       <c r="K148" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L148" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M148" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.45">
@@ -3850,13 +3874,13 @@
         <v>124</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C149" s="32" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D149" s="33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>172</v>
@@ -3867,16 +3891,16 @@
     </row>
     <row r="150" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A150" s="34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B150" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D150" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
@@ -3884,16 +3908,16 @@
     </row>
     <row r="151" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A151" s="34" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B151" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C151" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
@@ -3901,16 +3925,16 @@
     </row>
     <row r="152" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A152" s="34" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B152" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D152" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
@@ -3918,16 +3942,16 @@
     </row>
     <row r="153" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A153" s="34" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B153" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C153" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D153" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
@@ -3938,13 +3962,13 @@
         <v>125</v>
       </c>
       <c r="B154" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C154" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D154" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.45">
@@ -3952,16 +3976,16 @@
         <v>126</v>
       </c>
       <c r="B155" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D155" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K155" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.45">
@@ -3969,13 +3993,13 @@
         <v>127</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D156" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.45">
@@ -3983,24 +4007,24 @@
         <v>128</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="158" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A158" s="34" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D158" s="42"/>
       <c r="E158" s="8"/>
@@ -4012,7 +4036,7 @@
         <v>129</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D159" s="42"/>
       <c r="E159" s="8"/>
@@ -4024,13 +4048,13 @@
         <v>130</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D160" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.45">
@@ -4038,13 +4062,13 @@
         <v>131</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C161" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.45">
@@ -4052,13 +4076,13 @@
         <v>132</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D162" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J162" s="6" t="s">
         <v>173</v>
@@ -4069,24 +4093,24 @@
         <v>133</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D163" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="164" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A164" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C164" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="8"/>
@@ -4095,13 +4119,13 @@
     </row>
     <row r="165" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A165" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C165" s="35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D165" s="42"/>
       <c r="E165" s="8"/>
@@ -4113,7 +4137,7 @@
         <v>134</v>
       </c>
       <c r="B166" s="41" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D166" s="42"/>
       <c r="E166" s="8"/>
@@ -4125,7 +4149,7 @@
         <v>135</v>
       </c>
       <c r="B167" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D167" s="42"/>
       <c r="E167" s="8"/>
@@ -4134,10 +4158,10 @@
     </row>
     <row r="168" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A168" s="34" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B168" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D168" s="42"/>
       <c r="E168" s="8"/>
@@ -4149,28 +4173,28 @@
         <v>136</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D169" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E169" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G169" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K169" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L169" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M169" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.45">
@@ -4178,10 +4202,10 @@
         <v>137</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D170" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.45">
@@ -4200,10 +4224,10 @@
         <v>1</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D172" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.45">
@@ -4214,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D173" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.45">
@@ -4228,10 +4252,10 @@
         <v>1</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D174" s="23" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.45">
@@ -4242,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D175" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.45">
@@ -4358,10 +4382,10 @@
         <v>158</v>
       </c>
       <c r="C189" s="39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D189" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
@@ -4372,10 +4396,10 @@
         <v>158</v>
       </c>
       <c r="C190" s="39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.45">
@@ -4386,10 +4410,10 @@
         <v>158</v>
       </c>
       <c r="C191" s="39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.45">
@@ -4400,12 +4424,12 @@
         <v>158</v>
       </c>
       <c r="D192" s="26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B193" s="20" t="s">
         <v>140</v>
@@ -4417,7 +4441,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B195" s="20">
         <f>COUNTIF($B$2:$B$194,"A")</f>
@@ -4458,7 +4482,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B196" s="20">
         <f>COUNTIF($B$2:$B$194,"AA")</f>
@@ -4499,7 +4523,7 @@
     </row>
     <row r="197" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A197" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B197" s="42">
         <f>COUNTIF($B$2:$B$194,"AAA")</f>
@@ -4532,7 +4556,7 @@
     </row>
     <row r="198" spans="1:10" s="37" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B198" s="48">
         <f>COUNTIF($B$2:$B$194,"shall")</f>
@@ -4573,7 +4597,7 @@
     </row>
     <row r="199" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A199" s="54" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B199" s="52">
         <f>COUNTIF($B$2:$B$194,"should")</f>
@@ -4754,85 +4778,105 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D496424F-F927-4DEE-86F6-CA0EBBA8D988}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="48.796875" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B1" s="61" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>-1</v>
+      </c>
+      <c r="B6" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>-1</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6" s="60" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>-2</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>-2</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="60" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="12" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" s="12" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A13" r:id="rId1" display="Wikipedia (2026)" xr:uid="{D62AB9EB-D87E-47CE-A8F5-08F7E0C2AB4F}"/>
+    <hyperlink ref="A15" r:id="rId1" display="Wikipedia (2026)" xr:uid="{D62AB9EB-D87E-47CE-A8F5-08F7E0C2AB4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4848,7 +4892,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
@@ -4858,7 +4902,7 @@
     </row>
     <row r="3" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">

--- a/test-automation/EN301549v4.1.1-web-automation-matrix.en.xlsx
+++ b/test-automation/EN301549v4.1.1-web-automation-matrix.en.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\a11y-best-practices\test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2516E7A-E2E8-4C0E-8CB3-D2D42A22D362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EABF83-469B-4E6A-8394-767CC75D70B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5130" yWindow="-21720" windowWidth="51840" windowHeight="21840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14116" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foreword" sheetId="1" r:id="rId1"/>
@@ -120,6 +120,40 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gottfried Zimmermann</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{4340225E-0A54-4AFE-B75A-83F4074D0022}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Gottfried Zimmermann:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+True negatives are ignored for the purpose of averaging over multiple instances of criteria applications.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="282">
   <si>
@@ -963,24 +997,31 @@
     <t>Meaning wrt negatives</t>
   </si>
   <si>
-    <t>True negative</t>
-  </si>
-  <si>
     <t>False positive, with no or irrelevant/false location information</t>
   </si>
   <si>
     <t>This scale is understood as interval scale, i.e. arithmetic means can be computed.</t>
+  </si>
+  <si>
+    <t>(True negatives)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1128,6 +1169,19 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1233,148 +1287,149 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1747,7 +1802,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>164</v>
       </c>
@@ -4777,7 +4832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D496424F-F927-4DEE-86F6-CA0EBBA8D988}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D496424F-F927-4DEE-86F6-CA0EBBA8D988}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4816,8 +4871,8 @@
       <c r="A5">
         <v>0</v>
       </c>
-      <c r="C5" s="60" t="s">
-        <v>279</v>
+      <c r="C5" s="62" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -4836,7 +4891,7 @@
         <v>-2</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -4846,7 +4901,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -4879,6 +4934,7 @@
     <hyperlink ref="A15" r:id="rId1" display="Wikipedia (2026)" xr:uid="{D62AB9EB-D87E-47CE-A8F5-08F7E0C2AB4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
